--- a/2.RCM/PLC_Inventory_Cost_RCM.xlsx
+++ b/2.RCM/PLC_Inventory_Cost_RCM.xlsx
@@ -558,10 +558,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評価対象: 株式会社テクノプレシジョン 親会社  /  評価期間: FY2025 (2025/4/1 - 2026/3/31)  /  作成日: 2026/04/10  /  作成者: 内部監査室</t>
-        </is>
-      </c>
-    </row>
+          <t>評価対象: デモA株式会社 親会社  /  評価期間: FY2025 (2025/4/1 - 2026/3/31)  /  作成日: 2026/04/10  /  作成者: 内部監査室</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1457,6 +1458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
